--- a/labs/data/outcomes.xlsx
+++ b/labs/data/outcomes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/louisodette/Documents/R_projects/osb_2025_site/labs/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B016297-DEB7-7E4C-B696-B2D8A68FE7B2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE1C922F-D27E-8343-A278-D8833BDFF44B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-1680" yWindow="-20940" windowWidth="38080" windowHeight="20800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="140" yWindow="760" windowWidth="34560" windowHeight="20800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Potential outcomes" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="40">
   <si>
     <t>Person</t>
   </si>
@@ -127,184 +127,26 @@
     <t>3. you're weighting over a POPULATION OF UNITS</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve">Vaccine is the treatment. And your </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>research question</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> is "what's the effect of the vaccine on mortality?"</t>
-    </r>
-  </si>
-  <si>
-    <t>The causal question can be three things:</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve">1. what the average effect of vaccines on mortality </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>for everyone</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>? That's the ATE</t>
-    </r>
-  </si>
-  <si>
-    <t>2. what's the average effect of vaccines on mortality for vaccinated people? That's the ATT</t>
-  </si>
-  <si>
-    <t>3. What's the average effect of vaccines on mortality for the unvaccinated? The's the ATU</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve">Which of those three average causal parameters </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>should</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> you be trying to estimate? </t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">It depends. </t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve">- It depends on which one you </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>personally</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> think is interesting</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve">- It depends on the </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>policy goal</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve">. Is the goal to vaccinate </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>everyone</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve">? </t>
-    </r>
-  </si>
-  <si>
-    <t>That is the ATE</t>
-  </si>
-  <si>
-    <t>- Is the goal though to understand if the vaccine helped the vaccinated?</t>
-  </si>
-  <si>
-    <t>That is the ATT</t>
+    <t>Gender</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>Assign males to treatment, females to control</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pick people with positive (&gt;= 0) treatment effects for treated </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -316,11 +158,13 @@
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -328,38 +172,37 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
-      <b/>
       <sz val="10"/>
-      <color theme="1"/>
+      <color theme="0"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -414,8 +257,14 @@
         <bgColor rgb="FFFF0000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -475,11 +324,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -526,6 +384,15 @@
     <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -744,537 +611,767 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:M55"/>
+  <dimension ref="A1:T56"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="4" max="4" width="14.5" customWidth="1"/>
-    <col min="7" max="7" width="2.33203125" customWidth="1"/>
-    <col min="11" max="11" width="36.5" customWidth="1"/>
-    <col min="12" max="12" width="27.33203125" customWidth="1"/>
+    <col min="2" max="2" width="7.1640625" customWidth="1"/>
+    <col min="3" max="4" width="11.83203125" customWidth="1"/>
+    <col min="5" max="5" width="14.5" customWidth="1"/>
+    <col min="8" max="8" width="2.33203125" customWidth="1"/>
+    <col min="12" max="12" width="36.5" customWidth="1"/>
+    <col min="13" max="13" width="2.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="28" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="N1" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="O1" s="28"/>
+      <c r="P1" s="28"/>
+      <c r="Q1" s="28"/>
+      <c r="R1" s="28"/>
+      <c r="S1" s="28"/>
+      <c r="T1" s="28"/>
+    </row>
+    <row r="2" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B2" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="G2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="6"/>
-      <c r="H1" s="7" t="s">
+      <c r="H2" s="6"/>
+      <c r="I2" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="8" t="s">
+      <c r="M2" s="6"/>
+      <c r="N2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="O2" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="R2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="T2" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="9">
+      <c r="B3" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="C3" s="9">
         <v>15</v>
       </c>
-      <c r="C2" s="9">
+      <c r="D3" s="9">
         <v>12</v>
       </c>
-      <c r="D2" s="10">
-        <f t="shared" ref="D2:D11" si="0">B2-C2</f>
-        <v>3</v>
-      </c>
-      <c r="E2" s="11">
-        <f t="shared" ref="E2:E11" si="1">F2*B2+(1-F2)*C2</f>
+      <c r="E3" s="10"/>
+      <c r="F3" s="11">
+        <f t="shared" ref="F3:F12" si="0">G3*C3+(1-G3)*D3</f>
+        <v>12</v>
+      </c>
+      <c r="G3" s="12"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="J3" s="14"/>
+      <c r="K3" s="14"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="O3" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="P3" s="9">
         <v>15</v>
       </c>
-      <c r="F2" s="12">
-        <v>1</v>
-      </c>
-      <c r="G2" s="6"/>
-      <c r="H2" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="I2" s="14"/>
-      <c r="J2" s="14"/>
-      <c r="L2" s="15"/>
-    </row>
-    <row r="3" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="9">
+      <c r="Q3" s="9">
+        <v>12</v>
+      </c>
+      <c r="R3" s="10"/>
+      <c r="S3" s="11">
+        <f t="shared" ref="S3:S12" si="1">T3*P3+(1-T3)*Q3</f>
+        <v>12</v>
+      </c>
+      <c r="T3" s="12"/>
+    </row>
+    <row r="4" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" s="9">
         <v>5</v>
       </c>
-      <c r="C3" s="9">
+      <c r="D4" s="9">
         <v>10</v>
       </c>
-      <c r="D3" s="10">
+      <c r="E4" s="10"/>
+      <c r="F4" s="11">
         <f t="shared" si="0"/>
-        <v>-5</v>
-      </c>
-      <c r="E3" s="11">
+        <v>10</v>
+      </c>
+      <c r="G4" s="12"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="J4" s="14"/>
+      <c r="M4" s="6"/>
+      <c r="N4" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="O4" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="P4" s="9">
+        <v>5</v>
+      </c>
+      <c r="Q4" s="9">
+        <v>10</v>
+      </c>
+      <c r="R4" s="10"/>
+      <c r="S4" s="11">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="F3" s="12">
-        <v>0</v>
-      </c>
-      <c r="G3" s="6"/>
-      <c r="H3" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="I3" s="14"/>
-      <c r="L3" s="15"/>
-    </row>
-    <row r="4" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="8" t="s">
+      <c r="T4" s="12"/>
+    </row>
+    <row r="5" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="9">
+      <c r="B5" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" s="9">
         <v>17</v>
       </c>
-      <c r="C4" s="9">
+      <c r="D5" s="9">
         <v>11</v>
       </c>
-      <c r="D4" s="10">
+      <c r="E5" s="10"/>
+      <c r="F5" s="11">
         <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="E4" s="11">
+        <v>11</v>
+      </c>
+      <c r="G5" s="12"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="J5" s="14"/>
+      <c r="K5" s="14"/>
+      <c r="L5" s="14"/>
+      <c r="M5" s="6"/>
+      <c r="N5" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="O5" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="P5" s="9">
+        <v>17</v>
+      </c>
+      <c r="Q5" s="9">
+        <v>11</v>
+      </c>
+      <c r="R5" s="10"/>
+      <c r="S5" s="11">
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
-      <c r="F4" s="12">
-        <v>0</v>
-      </c>
-      <c r="G4" s="6"/>
-      <c r="H4" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="I4" s="14"/>
-      <c r="J4" s="14"/>
-      <c r="K4" s="14"/>
-    </row>
-    <row r="5" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="8" t="s">
+      <c r="T5" s="12"/>
+    </row>
+    <row r="6" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="9">
+      <c r="B6" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" s="9">
         <v>10</v>
       </c>
-      <c r="C5" s="9">
-        <v>9</v>
-      </c>
-      <c r="D5" s="10">
+      <c r="D6" s="9">
+        <v>9</v>
+      </c>
+      <c r="E6" s="10"/>
+      <c r="F6" s="11">
         <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="G6" s="12"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="M6" s="6"/>
+      <c r="N6" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="O6" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="P6" s="9">
+        <v>10</v>
+      </c>
+      <c r="Q6" s="9">
+        <v>9</v>
+      </c>
+      <c r="R6" s="10"/>
+      <c r="S6" s="11">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="T6" s="12"/>
+    </row>
+    <row r="7" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" s="9">
+        <v>9</v>
+      </c>
+      <c r="D7" s="9">
+        <v>9</v>
+      </c>
+      <c r="E7" s="10"/>
+      <c r="F7" s="11">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="G7" s="12"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="M7" s="6"/>
+      <c r="N7" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="O7" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="P7" s="9">
+        <v>9</v>
+      </c>
+      <c r="Q7" s="9">
+        <v>9</v>
+      </c>
+      <c r="R7" s="10"/>
+      <c r="S7" s="11">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="T7" s="12"/>
+    </row>
+    <row r="8" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" s="9">
         <v>1</v>
       </c>
-      <c r="E5" s="11">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="F5" s="12">
+      <c r="D8" s="9">
+        <v>5</v>
+      </c>
+      <c r="E8" s="10"/>
+      <c r="F8" s="11">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="G8" s="12"/>
+      <c r="H8" s="6"/>
+      <c r="J8" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="K8" s="17"/>
+      <c r="L8" s="15"/>
+      <c r="M8" s="6"/>
+      <c r="N8" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="O8" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="P8" s="9">
         <v>1</v>
       </c>
-      <c r="G5" s="6"/>
-      <c r="H5" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="L5" s="15"/>
-    </row>
-    <row r="6" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" s="9">
-        <v>9</v>
-      </c>
-      <c r="C6" s="9">
-        <v>9</v>
-      </c>
-      <c r="D6" s="10">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E6" s="11">
-        <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-      <c r="F6" s="12">
-        <v>1</v>
-      </c>
-      <c r="G6" s="6"/>
-      <c r="H6" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="M6" s="15"/>
-    </row>
-    <row r="7" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" s="9">
-        <v>1</v>
-      </c>
-      <c r="C7" s="9">
+      <c r="Q8" s="9">
         <v>5</v>
       </c>
-      <c r="D7" s="10">
-        <f t="shared" si="0"/>
-        <v>-4</v>
-      </c>
-      <c r="E7" s="11">
+      <c r="R8" s="10"/>
+      <c r="S8" s="11">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="F7" s="12">
-        <v>0</v>
-      </c>
-      <c r="G7" s="6"/>
-      <c r="I7" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="J7" s="17"/>
-      <c r="K7" s="15"/>
-    </row>
-    <row r="8" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="8" t="s">
+      <c r="T8" s="12"/>
+    </row>
+    <row r="9" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="9">
+      <c r="B9" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" s="9">
         <v>13</v>
       </c>
-      <c r="C8" s="9">
-        <v>9</v>
-      </c>
-      <c r="D8" s="10">
+      <c r="D9" s="9">
+        <v>9</v>
+      </c>
+      <c r="E9" s="10"/>
+      <c r="F9" s="11">
         <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="E8" s="11">
+        <v>9</v>
+      </c>
+      <c r="G9" s="12"/>
+      <c r="H9" s="6"/>
+      <c r="J9" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="K9" s="18"/>
+      <c r="L9" s="15"/>
+      <c r="M9" s="6"/>
+      <c r="N9" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="O9" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="P9" s="9">
+        <v>13</v>
+      </c>
+      <c r="Q9" s="9">
+        <v>9</v>
+      </c>
+      <c r="R9" s="10"/>
+      <c r="S9" s="11">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="F8" s="12">
-        <v>0</v>
-      </c>
-      <c r="G8" s="6"/>
-      <c r="I8" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="J8" s="18"/>
-      <c r="K8" s="15"/>
-    </row>
-    <row r="9" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="8" t="s">
+      <c r="T9" s="12"/>
+    </row>
+    <row r="10" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="9">
+      <c r="B10" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="9">
         <v>10</v>
       </c>
-      <c r="C9" s="9">
+      <c r="D10" s="9">
         <v>8</v>
       </c>
-      <c r="D9" s="10">
+      <c r="E10" s="10"/>
+      <c r="F10" s="11">
         <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="E9" s="11">
-        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="G10" s="12"/>
+      <c r="H10" s="6"/>
+      <c r="J10" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="L10" s="15"/>
+      <c r="M10" s="6"/>
+      <c r="N10" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="O10" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="P10" s="9">
         <v>10</v>
       </c>
-      <c r="F9" s="12">
-        <v>1</v>
-      </c>
-      <c r="G9" s="6"/>
-      <c r="I9" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="K9" s="15"/>
-      <c r="L9" s="15"/>
-    </row>
-    <row r="10" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" s="9">
-        <v>9</v>
-      </c>
-      <c r="C10" s="9">
-        <v>12</v>
-      </c>
-      <c r="D10" s="10">
-        <f t="shared" si="0"/>
-        <v>-3</v>
-      </c>
-      <c r="E10" s="11">
-        <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-      <c r="F10" s="12">
-        <v>1</v>
-      </c>
-      <c r="G10" s="6"/>
-      <c r="H10" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="L10" s="15"/>
-    </row>
-    <row r="11" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="B11" s="9">
+      <c r="Q10" s="9">
         <v>8</v>
       </c>
-      <c r="C11" s="9">
-        <v>15</v>
-      </c>
-      <c r="D11" s="10">
-        <f t="shared" si="0"/>
-        <v>-7</v>
-      </c>
-      <c r="E11" s="11">
+      <c r="R10" s="10"/>
+      <c r="S10" s="11">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="F11" s="12">
-        <v>1</v>
-      </c>
-      <c r="G11" s="6"/>
-      <c r="I11" s="16" t="s">
+      <c r="T10" s="12"/>
+    </row>
+    <row r="11" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="9">
+        <v>9</v>
+      </c>
+      <c r="D11" s="9">
+        <v>12</v>
+      </c>
+      <c r="E11" s="10"/>
+      <c r="F11" s="11">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="G11" s="12"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="M11" s="6"/>
+      <c r="N11" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="O11" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="P11" s="9">
+        <v>9</v>
+      </c>
+      <c r="Q11" s="9">
+        <v>12</v>
+      </c>
+      <c r="R11" s="10"/>
+      <c r="S11" s="11">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="T11" s="12"/>
+    </row>
+    <row r="12" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" s="9">
+        <v>8</v>
+      </c>
+      <c r="D12" s="9">
+        <v>15</v>
+      </c>
+      <c r="E12" s="10"/>
+      <c r="F12" s="11">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="G12" s="12"/>
+      <c r="H12" s="6"/>
+      <c r="J12" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="J11" s="17"/>
-      <c r="K11" s="15"/>
-      <c r="L11" s="15"/>
-    </row>
-    <row r="12" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C12" s="16" t="s">
+      <c r="K12" s="17"/>
+      <c r="L12" s="15"/>
+      <c r="M12" s="6"/>
+      <c r="N12" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="O12" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="P12" s="9">
+        <v>8</v>
+      </c>
+      <c r="Q12" s="9">
+        <v>15</v>
+      </c>
+      <c r="R12" s="10"/>
+      <c r="S12" s="11">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="T12" s="12"/>
+    </row>
+    <row r="13" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D13" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="D12" s="10">
-        <f>(SUM(D2:D11)/10)</f>
-        <v>-0.3</v>
-      </c>
-      <c r="E12" s="11"/>
-      <c r="G12" s="6"/>
-      <c r="I12" s="7" t="s">
+      <c r="E13" s="10"/>
+      <c r="F13" s="11"/>
+      <c r="H13" s="6"/>
+      <c r="J13" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="J12" s="18"/>
-      <c r="K12" s="15"/>
-    </row>
-    <row r="13" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="19"/>
-      <c r="C13" s="20" t="s">
+      <c r="K13" s="18"/>
+      <c r="L13" s="15"/>
+      <c r="M13" s="6"/>
+      <c r="Q13" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="R13" s="10"/>
+      <c r="S13" s="11"/>
+    </row>
+    <row r="14" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="19"/>
+      <c r="B14" s="19"/>
+      <c r="D14" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="D13" s="10">
-        <f>(SUM(D11,D10,D9,D6,D5,D2)/6)</f>
-        <v>-0.66666666666666663</v>
-      </c>
-      <c r="E13" s="11"/>
-      <c r="G13" s="6"/>
-      <c r="I13" s="7" t="s">
+      <c r="E14" s="10"/>
+      <c r="F14" s="11"/>
+      <c r="H14" s="6"/>
+      <c r="J14" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="K13" s="15"/>
-    </row>
-    <row r="14" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C14" s="21" t="s">
+      <c r="L14" s="15"/>
+      <c r="M14" s="6"/>
+      <c r="N14" s="19"/>
+      <c r="O14" s="19"/>
+      <c r="Q14" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="R14" s="10"/>
+      <c r="S14" s="11"/>
+    </row>
+    <row r="15" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D15" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="D14" s="10">
-        <f>AVERAGE(D8,D7,D4,D3)</f>
-        <v>0.25</v>
-      </c>
-      <c r="E14" s="11"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="15" t="s">
+      <c r="E15" s="10"/>
+      <c r="F15" s="11"/>
+      <c r="H15" s="6"/>
+      <c r="I15" s="15" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C15" s="22" t="s">
+      <c r="M15" s="6"/>
+      <c r="Q15" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="R15" s="10"/>
+      <c r="S15" s="11"/>
+    </row>
+    <row r="16" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D16" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="D15" s="10">
-        <f>AVERAGE(F2:F11)</f>
-        <v>0.6</v>
-      </c>
-      <c r="E15" s="11"/>
-      <c r="G15" s="6"/>
-    </row>
-    <row r="16" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C16" s="23" t="s">
+      <c r="E16" s="10"/>
+      <c r="F16" s="11"/>
+      <c r="H16" s="6"/>
+      <c r="M16" s="6"/>
+      <c r="Q16" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="R16" s="10"/>
+      <c r="S16" s="11"/>
+    </row>
+    <row r="17" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D17" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="10">
-        <f>1-D15</f>
-        <v>0.4</v>
-      </c>
-      <c r="E16" s="11"/>
-    </row>
-    <row r="17" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C17" s="15" t="s">
+      <c r="E17" s="10"/>
+      <c r="F17" s="11"/>
+      <c r="Q17" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="R17" s="10"/>
+      <c r="S17" s="11"/>
+    </row>
+    <row r="18" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D18" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="D17" s="10"/>
-      <c r="E17" s="11"/>
-      <c r="H17" s="15" t="s">
+      <c r="E18" s="10"/>
+      <c r="F18" s="11"/>
+      <c r="I18" s="15" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C18" s="15" t="s">
+      <c r="Q18" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="R18" s="10"/>
+      <c r="S18" s="11"/>
+    </row>
+    <row r="19" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D19" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="D18" s="10"/>
-      <c r="E18" s="11"/>
-      <c r="I18" s="15" t="s">
+      <c r="E19" s="10"/>
+      <c r="F19" s="11"/>
+      <c r="J19" s="15" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C19" s="15" t="s">
+      <c r="Q19" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="R19" s="10"/>
+      <c r="S19" s="11"/>
+    </row>
+    <row r="20" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D20" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="D19" s="10"/>
-      <c r="E19" s="11"/>
-      <c r="I19" s="15" t="s">
+      <c r="E20" s="10"/>
+      <c r="F20" s="11"/>
+      <c r="J20" s="15" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="20" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="24"/>
-      <c r="B20" s="25"/>
-      <c r="C20" s="25"/>
-      <c r="D20" s="19"/>
-      <c r="I20" s="15" t="s">
+      <c r="Q20" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="R20" s="10"/>
+      <c r="S20" s="11"/>
+    </row>
+    <row r="21" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A21" s="24"/>
+      <c r="B21" s="24"/>
+      <c r="C21" s="25"/>
+      <c r="D21" s="25"/>
+      <c r="E21" s="19"/>
+      <c r="J21" s="15" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="15"/>
-      <c r="H22" s="15"/>
-    </row>
-    <row r="23" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A23" s="15"/>
       <c r="B23" s="15"/>
       <c r="I23" s="15"/>
     </row>
-    <row r="24" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B24" s="15"/>
-    </row>
-    <row r="27" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="15" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="I28" s="15"/>
-    </row>
-    <row r="29" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B29" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="I29" s="15"/>
-    </row>
-    <row r="30" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B30" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="I30" s="15"/>
-    </row>
-    <row r="31" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B31" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="I31" s="15"/>
-    </row>
-    <row r="33" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="15" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B34" s="15" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C35" s="15" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C36" s="15" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D37" s="15" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C38" s="15" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D39" s="15" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A41" s="15"/>
-    </row>
-    <row r="42" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C24" s="15"/>
+      <c r="J24" s="15"/>
+    </row>
+    <row r="25" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C25" s="15"/>
+    </row>
+    <row r="28" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A28" s="15"/>
+      <c r="B28" s="15"/>
+    </row>
+    <row r="29" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A29" s="15"/>
+      <c r="B29" s="15"/>
+      <c r="J29" s="15"/>
+    </row>
+    <row r="30" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C30" s="15"/>
+      <c r="J30" s="15"/>
+    </row>
+    <row r="31" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C31" s="15"/>
+      <c r="J31" s="15"/>
+    </row>
+    <row r="32" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C32" s="15"/>
+      <c r="J32" s="15"/>
+    </row>
+    <row r="34" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A34" s="15"/>
+      <c r="B34" s="15"/>
+    </row>
+    <row r="35" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C35" s="15"/>
+    </row>
+    <row r="36" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D36" s="15"/>
+    </row>
+    <row r="37" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D37" s="15"/>
+    </row>
+    <row r="38" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="E38" s="15"/>
+    </row>
+    <row r="39" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D39" s="15"/>
+    </row>
+    <row r="40" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="E40" s="15"/>
+    </row>
+    <row r="42" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A42" s="15"/>
       <c r="B42" s="15"/>
     </row>
-    <row r="43" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B43" s="15"/>
-    </row>
-    <row r="44" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B44" s="15"/>
-    </row>
-    <row r="46" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B46" s="15"/>
-    </row>
-    <row r="49" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A49" s="15"/>
-    </row>
-    <row r="50" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C43" s="15"/>
+    </row>
+    <row r="44" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C44" s="15"/>
+    </row>
+    <row r="45" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C45" s="15"/>
+    </row>
+    <row r="47" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C47" s="15"/>
+    </row>
+    <row r="50" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A50" s="15"/>
       <c r="B50" s="15"/>
     </row>
-    <row r="51" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B51" s="15"/>
-    </row>
-    <row r="52" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C51" s="15"/>
+    </row>
+    <row r="52" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C52" s="15"/>
     </row>
-    <row r="53" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D53" s="15"/>
     </row>
-    <row r="54" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B54" s="15"/>
-    </row>
-    <row r="55" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B55" s="15"/>
+    <row r="54" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="E54" s="15"/>
+    </row>
+    <row r="55" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C55" s="15"/>
+    </row>
+    <row r="56" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C56" s="15"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="N1:T1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>